--- a/docs/ubwc_enc_reg_table.xlsx
+++ b/docs/ubwc_enc_reg_table.xlsx
@@ -66,7 +66,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I79"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -165,12 +165,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IP version</t>
+          <t>IP version register.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Returns fixed value 32'h0001_0000</t>
+          <t>Read once after reset to confirm software/RTL compatibility.</t>
         </is>
       </c>
     </row>
@@ -212,12 +212,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RTL date</t>
+          <t>RTL date register.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Returns fixed value 32'h2026_0406</t>
+          <t>Read once after reset to confirm software/RTL compatibility.</t>
         </is>
       </c>
     </row>
@@ -259,12 +259,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Enable UBWC encoding</t>
+          <t>Encoder UBWC enable.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Recommended as the final write in the tile address configuration group</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -306,12 +306,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Level-1 bank swizzle enable</t>
+          <t>Level-1 bank swizzle enable.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -353,12 +353,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Level-2 bank swizzle enable</t>
+          <t>Level-2 bank swizzle enable.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -400,12 +400,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Level-3 bank swizzle enable</t>
+          <t>Level-3 bank swizzle enable.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -447,12 +447,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Highest bank bit configuration</t>
+          <t>Highest bank bit.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bank spread enable</t>
+          <t>Bank spread enable.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4-line tile format enable</t>
+          <t>4-line tile format enable. RGBA=1, YUV420=0.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Program by format: RGBA8888/RGBA1010102=1; YUV420_8/YUV420_10=0. Recommended to write this register before committing REG_TILE_CFG0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -588,12 +588,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>RGBA 2:1 lossy format select</t>
+          <t>RGBA8888 lossy 2:1 layout select.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tile pitch in 16-byte units</t>
+          <t>Tile pitch in 16-byte units. RTL exports {1'b0, bits[26:16]}.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Write pitch_reg=align_up(width*bytes_per_pixel, tile_w*4*bytes_per_pixel)/16. bytes_per_pixel: RGBA8888=4, RGBA1010102=4, YUV420_8=1, YUV420_10=2. This register value is in 16-byte units, not bytes; effective field width is 11 bits. Example NV12 1996x1074: align_up(1996*1,32*4*1)=2048 bytes, tile_pitch=2048/16=128.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Encoded CI input type</t>
+          <t>CI input type. Current encoder software should write 1.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Encoding: 0=linear data, 1=tiled data. Fixed value for current encoder path: software should write 1. Recommended as the final write in the CI configuration group.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Encoded CI alen configuration</t>
+          <t>CI ALEN setting. Current software writes 3'd7.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Fixed value. Software should write 3'd7.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG0</t>
+          <t>REG_ENC_CI_CFG1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>enc_ci_lossy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>CI lossy enable.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0; current encoder format is configured by REG_OTF_CFG0.otf_cfg_format.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG0</t>
+          <t>REG_ENC_CI_CFG2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>enc_ci_ubwc_cfg_0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0; forced PCM is generated dynamically by the OTF path.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG1</t>
+          <t>REG_ENC_CI_CFG2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SB_WIDTH-1:0</t>
+          <t>5:3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>enc_ci_sb</t>
+          <t>enc_ci_ubwc_cfg_1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG1</t>
+          <t>REG_ENC_CI_CFG2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9:6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>enc_ci_lossy</t>
+          <t>enc_ci_ubwc_cfg_2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Encoded CI lossy enable</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_0</t>
+          <t>enc_ci_ubwc_cfg_3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5:3</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_1</t>
+          <t>enc_ci_ubwc_cfg_4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1048,22 +1048,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9:6</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_2</t>
+          <t>enc_ci_ubwc_cfg_5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1095,22 +1095,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_3</t>
+          <t>enc_ci_ubwc_cfg_6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1142,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>25:24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_4</t>
+          <t>enc_ci_ubwc_cfg_7</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1189,22 +1189,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>27:26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_5</t>
+          <t>enc_ci_ubwc_cfg_8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1236,22 +1236,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>30:28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_6</t>
+          <t>enc_ci_ubwc_cfg_9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG2</t>
+          <t>REG_ENC_CI_CFG3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1283,22 +1283,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25:24</t>
+          <t>5:0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_7</t>
+          <t>enc_ci_ubwc_cfg_10</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG2</t>
+          <t>REG_ENC_CI_CFG3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27:26</t>
+          <t>13:8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_8</t>
+          <t>enc_ci_ubwc_cfg_11</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG2</t>
+          <t>REG_OTF_CFG0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1377,22 +1377,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>30:28</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_9</t>
+          <t>otf_cfg_format</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Input format: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>0x001c</t>
+          <t>0x0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG3</t>
+          <t>REG_OTF_CFG1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1424,22 +1424,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_10</t>
+          <t>otf_cfg_width</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Input image width in pixels.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>0x001c</t>
+          <t>0x0024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG3</t>
+          <t>REG_OTF_CFG1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1471,22 +1471,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13:8</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_11</t>
+          <t>otf_cfg_height</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Input/stored image height in pixels.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>0x0020</t>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG0</t>
+          <t>REG_OTF_CFG2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1518,22 +1518,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>otf_cfg_format</t>
+          <t>otf_cfg_tile_w</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Input OTF format</t>
+          <t>Tile width in pixels. RGBA=16, YUV420=32.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Recommended as the final write in the OTF configuration group. Format code: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>0x0024</t>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG1</t>
+          <t>REG_OTF_CFG2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1565,22 +1565,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>otf_cfg_width</t>
+          <t>otf_cfg_tile_h</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Input image width in pixels</t>
+          <t>Tile height in pixels. RGBA=4, NV12=8, P010=4.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Software should use this width to calculate tile columns: ceil(width / tile_w).</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>0x0024</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG1</t>
+          <t>REG_OTF_CFG3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1612,22 +1612,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>otf_cfg_height</t>
+          <t>otf_cfg_y_tile_cols</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Input image height in pixels</t>
+          <t>Y tile column count. RGBA formats use this field for RGBA tile columns.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Program stored/input frame height. For YUV420, UV plane uses half-height internally.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>0x0028</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG2</t>
+          <t>REG_OTF_CFG3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1659,22 +1659,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>otf_cfg_tile_w</t>
+          <t>otf_cfg_uv_tile_cols</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tile width in pixels</t>
+          <t>UV tile column count. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Program by format: RGBA8888/RGBA1010102=16; YUV420_8/YUV420_10=32.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>0x0028</t>
+          <t>0x0030</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG2</t>
+          <t>REG_META_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1706,22 +1706,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>otf_cfg_tile_h</t>
+          <t>meta_y_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tile height in pixels</t>
+          <t>Y metadata base address low word. RGBA formats use this slot for RGBA metadata.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Program by format: RGBA8888/RGBA1010102=4; YUV420_8/YUV420_10=8.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>0x002c</t>
+          <t>0x0034</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG3</t>
+          <t>REG_META_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1753,22 +1753,22 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>otf_cfg_y_tile_cols</t>
+          <t>meta_y_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Y tile column count</t>
+          <t>Y metadata base address high word. RGBA formats use this slot for RGBA metadata.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Program by format: RGBA formats=ceil(width/16); YUV formats Y=ceil(width/32).</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>0x002c</t>
+          <t>0x0038</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG3</t>
+          <t>REG_TILE_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>otf_cfg_uv_tile_cols</t>
+          <t>y_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>UV tile column count</t>
+          <t>Y compressed tile/pixel data base address low word. RGBA formats use this slot for RGBA data.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Program by format: RGBA formats=0; YUV formats UV=ceil(width/32).</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>0x0030</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_LO</t>
+          <t>REG_TILE_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[31:0]</t>
+          <t>y_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y metadata base address</t>
+          <t>Y compressed tile/pixel data base address high word. RGBA formats use this slot for RGBA data.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>For RGBA formats, use this slot for RGBA metadata. For YUV formats, program Y metadata start. Example NV12 1996x1074 base=0xA00000: Y meta_base=0xA00000, Y meta_pitch=64, Y meta_size=0x3000.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>0x0034</t>
+          <t>0x0040</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_HI</t>
+          <t>REG_META_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[63:32]</t>
+          <t>meta_uv_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y metadata base address</t>
+          <t>UV metadata base address low word. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>0x0038</t>
+          <t>0x0044</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_LO</t>
+          <t>REG_META_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[31:0]</t>
+          <t>meta_uv_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y compressed data base address</t>
+          <t>UV metadata base address high word. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>For RGBA formats, use this slot for RGBA compressed data. For YUV formats, program Y pixel/tile data start. Example NV12 1996x1074: Y tile_base=0xA03000.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>0x003c</t>
+          <t>0x0048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_HI</t>
+          <t>REG_TILE_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1993,17 +1993,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[63:32]</t>
+          <t>uv_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y compressed data base address</t>
+          <t>UV compressed tile/pixel data base address low word. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>0x0040</t>
+          <t>0x004c</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_LO</t>
+          <t>REG_TILE_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[31:0]</t>
+          <t>uv_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV metadata base address</t>
+          <t>UV compressed tile/pixel data base address high word. Writing this register commits the current four base addresses as one frame address set.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>For RGBA formats, write 0. Example NV12 1996x1074: UV_meta_base=0xC23000.</t>
+          <t>Per-frame configuration. This high-word write must be last and commits the four base addresses as one frame address group.</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>0x0044</t>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_HI</t>
+          <t>REG_META_ACTIVE_SIZE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[63:32]</t>
+          <t>meta_active_width_px</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV metadata base address</t>
+          <t>Metadata active width in pixels.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>0x0048</t>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_LO</t>
+          <t>REG_META_ACTIVE_SIZE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2129,22 +2129,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[31:0]</t>
+          <t>meta_active_height_px</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV compressed data base address</t>
+          <t>Metadata active height in pixels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>For RGBA formats, write 0. Example NV12 1996x1074: UV tile_base=0xC25000.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>0x004c</t>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_HI</t>
+          <t>REG_META_PITCH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[63:32]</t>
+          <t>meta_data_plane_pitch</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV compressed data base address</t>
+          <t>Metadata plane pitch configuration.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address and commits the current frame address set</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -2203,42 +2203,42 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>0x0050</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>REG_META_ACTIVE_SIZE</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>meta_active_width_px</t>
+          <t>enc_idle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metadata active-area width in pixels</t>
+          <t>Encoder idle input.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Writing 0 means using the full-frame width</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2250,42 +2250,42 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0x0050</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>REG_META_ACTIVE_SIZE</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>meta_active_height_px</t>
+          <t>enc_error</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metadata active-area height in pixels</t>
+          <t>Encoder error input.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Program metadata active height in pixels.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2297,42 +2297,42 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>REG_META_PITCH</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>meta_data_plane_pitch</t>
+          <t>otf_to_tile_busy</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metadata plane pitch</t>
+          <t>OTF-to-tile stage busy.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Write meta_data_plane_pitch=align_up((align_up(width, tile_w*4)+tile_w-1)/tile_w, 64), matching ubwc_demo.cpp. Current encoder meta address path uses meta_data_plane_pitch&lt;&lt;4 as byte stride. Example NV12 1996x1074 Y plane: align_up((align_up(1996,128)+32-1)/32,64)=64. UV plane example from contiguous layout also uses meta_pitch=64.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>enc_idle</t>
+          <t>otf_to_tile_overflow</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Encoder core idle status</t>
+          <t>OTF-to-tile FIFO overflow.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2411,22 +2411,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>enc_error</t>
+          <t>otf_err_bline</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Encoder core error status</t>
+          <t>Bad-line error.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2458,22 +2458,22 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>otf_to_tile_busy</t>
+          <t>otf_err_bframe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>OTF-to-tile busy status</t>
+          <t>Bad-frame error.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2505,22 +2505,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>otf_to_tile_overflow</t>
+          <t>meta_err_0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>OTF-to-tile FIFO overflow status</t>
+          <t>Metadata error bit 0.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2552,22 +2552,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>otf_err_bline</t>
+          <t>meta_err_1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>OTF input bad-line error status</t>
+          <t>Metadata error bit 1.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2599,22 +2599,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>otf_err_bframe</t>
+          <t>frame_done</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>OTF input bad-frame error status</t>
+          <t>Frame done status from wrapper.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>meta_err_0</t>
+          <t>addr_cfg_invalid</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metadata generator error 0 status</t>
+          <t>Current frame needs an address slot that is not configured.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Currently tied low</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>meta_err_1</t>
+          <t>addr_cfg_valid0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metadata generator error 1 status</t>
+          <t>Address slot 0 has a configured entry.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Currently tied low</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2740,22 +2740,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>frame_done</t>
+          <t>addr_cfg_valid1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Encoder frame done status</t>
+          <t>Address slot 1 has a configured entry.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Live frame done input from wrapper</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Encoder stage done bitmap</t>
+          <t>Encoder stage done bitmap.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RW/W1P</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IRQ enable</t>
+          <t>Interrupt enable.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Defaults to 1 after reset</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>IRQ clear pulse</t>
+          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Writing 1 generates an irq_clear pulse in the encoder clock domain; readback is 0</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -2938,17 +2938,863 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>IRQ pending status</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Synchronized into PCLK domain</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>irq_correct_pending</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Correct/frame-done interrupt pending.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>irq_error_pending</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Error interrupt pending.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REG_STATUS2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>irq_status</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>0x0068</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>REG_META_COUNT0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>meta_count0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>0x006c</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>REG_META_COUNT1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>meta_count1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>0x0070</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>REG_TILEADDR_COUNT0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>tileaddr_count0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>0x0074</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>REG_TILEADDR_COUNT1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>tileaddr_count1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>0x0078</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>REG_OTF_TILE_COUNT0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>otf_tile_count0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>0x007c</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>REG_OTF_TILE_COUNT1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>otf_tile_count1</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>0x0080</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>REG_OTF_DE_COUNT0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>otf_de_count0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>0x0084</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>REG_OTF_DE_COUNT1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>otf_de_count1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>0x0088</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>REG_OTF_LINE_COUNT0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>otf_line_count0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>0x008c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>REG_OTF_LINE_COUNT1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>otf_line_count1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>0x0090</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>0x0094</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>0x009c</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I61"/>
+  <autoFilter ref="A1:I79"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2977,7 +3823,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-07 04:34:29</t>
+          <t>2026-05-14 22:08:50</t>
         </is>
       </c>
     </row>
@@ -3501,7 +4347,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420=32x8。</t>
+          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420_8=32x8，YUV420_10=32x4。</t>
         </is>
       </c>
     </row>
@@ -3816,12 +4662,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Start OTF input stream</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENC 没有 APB start。上游 OTF vsync/hsync/de/data 进入后开始处理；fcnt[0] 用于选择地址 slot 和 sideband。</t>
+          <t>写 START token。地址写入只填充地址队列，不再作为 start 标志；写 START 后再送入对应 OTF vsync/hsync/de/data。</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4955,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value.</t>
+          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value. A separate IRQ_CTRL[5] start write is still required for the frame.</t>
         </is>
       </c>
     </row>
@@ -4157,7 +5003,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Correct IRQ is produced near the output hsync of the 4th line before frame end. Error IRQ is produced when an error condition is latched.</t>
+          <t>Correct IRQ/frame_done is produced after the final valid frame output/data completion event. Error IRQ is produced when an error condition is latched.</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_enc_reg_table.xlsx
+++ b/docs/ubwc_enc_reg_table.xlsx
@@ -66,7 +66,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metadata error bit 0.</t>
+          <t>Metadata co-buffer overflow error.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metadata error bit 1.</t>
+          <t>Metadata tile-order error.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>REG_STATUS1</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2787,22 +2787,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7:0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stage_done</t>
+          <t>addr_cfg_overflow</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Encoder stage done bitmap.</t>
+          <t>Address slot FIFO overflow sticky status.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Read during runtime.</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2814,42 +2814,42 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>rst_drain_timeout</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Interrupt enable.</t>
+          <t>AXI drain timeout during encoder soft reset.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Configure after reset or when the interrupt policy changes.</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2861,42 +2861,42 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>W1P</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
+          <t>Encoder stage done bitmap.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Write 1 after software handles the interrupt; readback is 0.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2918,32 +2918,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Any pending interrupt.</t>
+          <t>Interrupt enable.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -2965,32 +2965,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Correct/frame-done interrupt pending.</t>
+          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -3022,17 +3022,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Error interrupt pending.</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>W1P</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
+          <t>Correct/frame-done interrupt pending.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+          <t>Error interrupt pending.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3143,42 +3143,42 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
         </is>
       </c>
     </row>
@@ -3190,12 +3190,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3210,22 +3210,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3754,47 +3754,141 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
+          <t>0x0094</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>dynamic</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3823,7 +3917,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-14 22:08:50</t>
+          <t>2026-05-19 09:33:12</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_enc_reg_table.xlsx
+++ b/docs/ubwc_enc_reg_table.xlsx
@@ -66,7 +66,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CI input type. Current encoder software should write 1.</t>
+          <t>CI input type. 1=tiled data, 0=linear data. Register reset is 0; software should write 1 for the normal tiled UBWC path.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CI ALEN setting. Current software writes 3'd7.</t>
+          <t>CI ALEN setting. Register reset is 0; software should write 7 for the normal VIVO_ENC configuration.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[31:0]</t>
+          <t>meta_y_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[63:32]</t>
+          <t>meta_y_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[31:0]</t>
+          <t>y_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[63:32]</t>
+          <t>y_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[31:0]</t>
+          <t>meta_uv_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[63:32]</t>
+          <t>meta_uv_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[31:0]</t>
+          <t>uv_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[63:32]</t>
+          <t>uv_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2216,9 +2216,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2263,9 +2263,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2310,9 +2310,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2357,9 +2357,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2404,9 +2404,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2451,9 +2451,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2545,9 +2545,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2592,9 +2592,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2639,9 +2639,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Current frame needs an address slot that is not configured.</t>
+          <t>Sticky current-slot address-not-configured error. The ENC data path selects address slot0 or slot1 from the current frame fcnt[0]. When hardware checks the current slot address validity and the selected address FIFO is empty, active_addr_cfg_valid is 0, this bit is set and held, and the condition contributes to error IRQ. This means the current frame has no usable META/TILE base addresses. Software must submit the per-frame address group for the corresponding slot, confirm that the software buffer queue is aligned with fcnt[0], then clear the sticky status with REG_IRQ_CTRL[1] irq_clear; disabling enc_ubwc_en or hard reset also clears it.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2686,9 +2686,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2733,9 +2733,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2780,9 +2780,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Address slot FIFO overflow sticky status.</t>
+          <t>Sticky address-configuration FIFO overflow status. One frame address group contains four 64-bit base addresses: META Y, TILE Y, META UV, and TILE UV. Software commits one address group by writing REG_TILE_BASE_UV_HI. The APB block alternates committed groups into slot0/slot1 address FIFOs; each slot FIFO depth is 4. If the selected slot FIFO is full when the commit write occurs, the current address group is not pushed, this bit is set and held, and the condition contributes to error IRQ. Software should stop submitting new address groups, wait for existing frames to consume FIFO entries, clear the sticky bit with REG_IRQ_CTRL[1] irq_clear, and make sure the software buffer queue is aligned with the hardware address queue; if needed, disable enc_ubwc_en and reconfigure.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2827,9 +2827,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AXI drain timeout during encoder soft reset.</t>
+          <t>Sticky AXI drain timeout during encoder soft reset. Before asserting the internal soft reset, ENC stops issuing new AXI writes and waits for tile/meta AXI write outstanding transactions to drain. If idle is not reached within 16'hffff i_axi_clk cycles, this bit is set and held until REG_IRQ_CTRL[1] irq_clear or hard reset.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2874,9 +2874,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Interrupt enable.</t>
+          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3015,9 +3015,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3062,9 +3062,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3109,9 +3109,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3190,42 +3190,42 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>vsync_reset_en</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+          <t>When set, an input OTF VSYNC rising edge requests an encoder soft reset through the AXI-drain reset sequencer and re-arms the frame start token after reset release.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Configure according to the system policy. When set, ENC input VSYNC rising edges trigger a soft reset and re-arm frame start.</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3250,29 +3250,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3297,9 +3297,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3344,9 +3344,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3391,9 +3391,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3438,9 +3438,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3485,9 +3485,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3532,9 +3532,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3579,9 +3579,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3626,9 +3626,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3673,9 +3673,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3720,9 +3720,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3767,9 +3767,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3814,9 +3814,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3848,47 +3848,94 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3917,7 +3964,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 09:33:12</t>
+          <t>2026-05-21 13:09:24</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4232,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。复位默认 irq_enable=1。</t>
+          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。寄存器复位值为 0，软件需要写 1 才使能 IRQ。</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4424,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>最后写 CI_CFG0，配置 enc_ci_input_type 和 enc_ci_alen。当前软件通常写 input_type=1、alen=7。</t>
+          <t>最后写 CI_CFG0；寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 enc_ci_input_type=1、enc_ci_alen=7。</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4840,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应地址 slot 未配置。IRQ bit 区分 correct/error pending。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应 slot 没有可用地址配置，是 sticky 错误状态；软件补齐地址并确认队列对齐后，通过 REG_IRQ_CTRL[1] irq_clear 清除。IRQ bit 区分 correct/error pending。</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_enc_reg_table.xlsx
+++ b/docs/ubwc_enc_reg_table.xlsx
@@ -66,7 +66,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Y metadata base address low word. RGBA formats use this slot for RGBA metadata.</t>
+          <t>Y metadata base address low word. RGBA formats use this field for RGBA metadata.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Y metadata base address high word. RGBA formats use this slot for RGBA metadata.</t>
+          <t>Y metadata base address high word. RGBA formats use this field for RGBA metadata.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Y compressed tile/pixel data base address low word. RGBA formats use this slot for RGBA data.</t>
+          <t>Y compressed tile/pixel data base address low word. RGBA formats use this field for RGBA data.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Y compressed tile/pixel data base address high word. RGBA formats use this slot for RGBA data.</t>
+          <t>Y compressed tile/pixel data base address high word. RGBA formats use this field for RGBA data.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>UV compressed tile/pixel data base address high word. Writing this register commits the current four base addresses as one frame address set.</t>
+          <t>UV compressed tile/pixel data base address high word. Write this register last to mark the single working address set complete; START then latches it.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Per-frame configuration. This high-word write must be last and commits the four base addresses as one frame address group.</t>
+          <t>Configure when the address or layout changes. Write this high word last to mark the single address set complete, then issue START to latch it.</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sticky current-slot address-not-configured error. The ENC data path selects address slot0 or slot1 from the current frame fcnt[0]. When hardware checks the current slot address validity and the selected address FIFO is empty, active_addr_cfg_valid is 0, this bit is set and held, and the condition contributes to error IRQ. This means the current frame has no usable META/TILE base addresses. Software must submit the per-frame address group for the corresponding slot, confirm that the software buffer queue is aligned with fcnt[0], then clear the sticky status with REG_IRQ_CTRL[1] irq_clear; disabling enc_ubwc_en or hard reset also clears it.</t>
+          <t>Sticky single-address configuration error. It is set when the ENC data path checks an address configuration but the most recently START-latched META Y, TILE Y, META UV, and TILE UV base-address set is invalid. The condition contributes to error IRQ and remains set until REG_IRQ_CTRL[1] irq_clear, enc_ubwc_en disable, or hard reset.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>addr_cfg_valid0</t>
+          <t>addr_cfg_valid</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Address slot 0 has a configured entry.</t>
+          <t>The single META/TILE base-address set latched by the most recent START is valid. All frames reuse this set until software writes a new complete set and issues START again.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>addr_cfg_valid1</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Address slot 1 has a configured entry.</t>
+          <t>Reserved; reads as 0.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>addr_cfg_overflow</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sticky address-configuration FIFO overflow status. One frame address group contains four 64-bit base addresses: META Y, TILE Y, META UV, and TILE UV. Software commits one address group by writing REG_TILE_BASE_UV_HI. The APB block alternates committed groups into slot0/slot1 address FIFOs; each slot FIFO depth is 4. If the selected slot FIFO is full when the commit write occurs, the current address group is not pushed, this bit is set and held, and the condition contributes to error IRQ. Software should stop submitting new address groups, wait for existing frames to consume FIFO entries, clear the sticky bit with REG_IRQ_CTRL[1] irq_clear, and make sure the software buffer queue is aligned with the hardware address queue; if needed, disable enc_ubwc_en and reconfigure.</t>
+          <t>Reserved; reads as 0.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REG_STATUS1</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>7:0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stage_done</t>
+          <t>cfg_valid</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Encoder stage done bitmap.</t>
+          <t>Result of the most recent START configuration commit. Set when format, geometry, tile/metadata parameters, and the single address set are valid. When clear, ENC holds o_otf_ready low.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Read during runtime.</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2908,17 +2908,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2928,22 +2928,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
+          <t>Encoder stage done bitmap.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Configure after reset or when the interrupt policy changes.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>W1P</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2975,22 +2975,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
+          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Write 1 after software handles the interrupt; readback is 0.</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>W1P</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3022,22 +3022,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Any pending interrupt.</t>
+          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -3069,17 +3069,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Correct/frame-done interrupt pending.</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Error interrupt pending.</t>
+          <t>Correct/frame-done interrupt pending.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>W1P</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3163,22 +3163,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
+          <t>Error interrupt pending.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>W1P</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3210,22 +3210,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>vsync_reset_en</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>When set, an input OTF VSYNC rising edge requests an encoder soft reset through the AXI-drain reset sequencer and re-arms the frame start token after reset release.</t>
+          <t>Write 1 to validate and latch the complete ENC configuration snapshot. START does not reset the frame pipeline and does not start OTF processing. It must complete before the target VSYNC; a late commit applies from the next VSYNC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Configure according to the system policy. When set, ENC input VSYNC rising edges trigger a soft reset and re-arm frame start.</t>
+          <t>Write after static configuration and the single address set are ready; then read STATUS0[14] cfg_valid and STATUS0[10] addr_cfg_valid. START does not start a frame.</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3257,22 +3257,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+          <t>Reserved; reads as 0.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3304,22 +3304,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3895,47 +3895,94 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I82"/>
+  <autoFilter ref="A1:I83"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3964,7 +4011,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 13:09:24</t>
+          <t>2026-07-24 23:24:40</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -4623,7 +4670,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4633,7 +4680,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4648,14 +4695,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>配置下一帧地址组的 Y metadata base 低/高 32 bit；RGBA 使用该槽位存 RGBA metadata。</t>
+          <t>配置唯一一组 Y metadata base 低/高 32 bit；RGBA 使用该位置存 RGBA metadata。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4665,7 +4712,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4680,14 +4727,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>配置下一帧地址组的 Y tile data base 低/高 32 bit；RGBA 使用该槽位存 RGBA tile data。</t>
+          <t>配置唯一一组 Y tile data base 低/高 32 bit；RGBA 使用该位置存 RGBA tile data。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4697,7 +4744,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4712,14 +4759,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>配置 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
+          <t>配置唯一一组 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4729,7 +4776,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4744,14 +4791,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>配置 UV tile data base 低 32 bit，RGBA 写 0。</t>
+          <t>配置唯一一组 UV tile data base 低 32 bit，RGBA 写 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4761,7 +4808,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4776,14 +4823,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。本写入会提交当前四个 64 bit base address 为一组帧地址，必须最后写。</t>
+          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。该寄存器必须最后写，用于标记唯一工作地址组完整。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENC 启动</t>
+          <t>ENC 配置提交</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4793,7 +4840,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>每帧</t>
+          <t>静态配置或地址快照变化时</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4808,14 +4855,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>写 START token。地址写入只填充地址队列，不再作为 start 标志；写 START 后再送入对应 OTF vsync/hsync/de/data。</t>
+          <t>写 START 提交并锁存完整配置快照。START 不复位也不启动帧；读取 STATUS0[14] cfg_valid。START 必须在目标 VSYNC 前完成。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENC 监控</t>
+          <t>ENC 帧启动</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4825,7 +4872,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>运行中</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4835,121 +4882,121 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>READ 0x058/0x05C/0x060/0x064</t>
+          <t>输入 VSYNC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应 slot 没有可用地址配置，是 sticky 错误状态；软件补齐地址并确认队列对齐后，通过 REG_IRQ_CTRL[1] irq_clear 清除。IRQ bit 区分 correct/error pending。</t>
+          <t>每个 VSYNC 上升沿采样 cfg_valid，再触发 AXI drain 和全链路帧复位。采样有效时复位释放后自动运行；所有帧复用最近一次 START 锁存的唯一地址组。采样无效时整帧 o_otf_ready=0。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>ENC 监控</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>运行中</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>READ 0x058/0x05C/0x060/0x064</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。cfg_valid 表示 START 提交结果；addr_cfg_valid 表示唯一地址组已锁存且有效；IRQ bit 区分 correct/error pending。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>ENC 清中断</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>ENC</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>软件处理中断后</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>WRITE 0x060 bit[1]=1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>清除 ENC 中断 pending。统计计数仍可用于调试。</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>格式</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>编码</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>tile_w</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>tile_h</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>bpp</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>配置复用说明</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RGBA8888</t>
+          <t>格式</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>编码</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>tile_w</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>tile_h</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>bpp</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>格式和尺寸不变时，tile/OTF/meta geometry 可复用；每帧只更新 base address。</t>
+          <t>配置复用说明</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RGBA1010102</t>
+          <t>RGBA8888</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4969,83 +5016,115 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>几何规则同 RGBA8888；只换 buffer 地址时不需要重配 geometry。</t>
+          <t>格式、尺寸和输出 buffer 不变时，静态配置与唯一地址组均可持续复用。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YUV420_8/NV12</t>
+          <t>RGBA1010102</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1(Y),2(UV pair)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Y/UV 有独立 metadata/tile base；新 buffer 必须写每帧地址。</t>
+          <t>几何规则同 RGBA8888；更换 buffer 地址后重新写完整地址组并写 START。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>YUV420_8/NV12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1(Y),2(UV pair)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Y/UV 使用唯一一组独立 metadata/tile base；地址变化后重新写完整地址组并写 START。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>YUV420_10/P010</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2(Y),4(UV pair)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>tile count 规则按 P010 tile_h=4 计算，pitch 使用 16 bit component 存储计算。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
@@ -5079,12 +5158,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENC address slots</t>
+          <t>ENC single address set</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Two alternating address slots hold frame address sets for fcnt[0]=0/1. Each entry contains Y metadata base, Y tile base, UV metadata base, and UV tile base.</t>
+          <t>ENC has one address set containing Y metadata base, Y tile base, UV metadata base, and UV tile base. fcnt does not select an address.</t>
         </is>
       </c>
     </row>
@@ -5096,60 +5175,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value. A separate IRQ_CTRL[5] start write is still required for the frame.</t>
+          <t>Write REG_TILE_BASE_UV_HI @0x04C last to mark the working address set complete. Write IRQ_CTRL[5] START to validate and latch the complete snapshot, then check STATUS0[14] cfg_valid and STATUS0[10] addr_cfg_valid.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Contiguous UBWC layout</t>
+          <t>ENC frame reset</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>For YUV: Y metadata, Y tile data, UV metadata, UV tile data. For RGBA: RGBA metadata and RGBA tile data are enough; unused Y/UV partner bases may be written 0 as required by the wrapper path.</t>
+          <t>Every input VSYNC rising edge samples the committed configuration, requests AXI drain, and resets the frame pipeline. Processing starts automatically after reset release only when the sampled result is valid. Frames reuse the same latched addresses until a later START updates them.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Metadata pitch</t>
+          <t>Contiguous UBWC layout</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>meta_pitch=align_up(ceil(plane_width/tile_w),64). Metadata size aligns meta_pitch*align_up(tile_rows,16) to 4KB.</t>
+          <t>For YUV: Y metadata, Y tile data, UV metadata, UV tile data. For RGBA: RGBA metadata and RGBA tile data are enough; unused Y/UV partner bases may be written 0 as required by the wrapper path.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tile pitch</t>
+          <t>Metadata pitch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tile_pitch register is in 16-byte units. pixel_pitch=align_up(width*bpp,tile_w*4*bpp); tile_pitch=pixel_pitch/16.</t>
+          <t>meta_pitch=align_up(ceil(plane_width/tile_w),64). Metadata size aligns meta_pitch*align_up(tile_rows,16) to 4KB.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Tile pitch</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tile_pitch register is in 16-byte units. pixel_pitch=align_up(width*bpp,tile_w*4*bpp); tile_pitch=pixel_pitch/16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>IRQ timing</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Correct IRQ/frame_done is produced after the final valid frame output/data completion event. Error IRQ is produced when an error condition is latched.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>